--- a/Group 5_ CMARCH1_GanttChart.xlsx
+++ b/Group 5_ CMARCH1_GanttChart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76785BC8-424B-4A05-B360-84D2D6273892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1741AE24-B46C-432F-A973-19F484046BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,6 +872,9 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -880,9 +883,6 @@
     </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E3" s="25">
         <f ca="1">TODAY()</f>
-        <v>46122</v>
+        <v>46146</v>
       </c>
       <c r="F3" s="26"/>
     </row>
@@ -1529,733 +1529,733 @@
         <v>8</v>
       </c>
       <c r="E4" s="24">
-        <v>1</v>
-      </c>
-      <c r="I4" s="62">
+        <v>3</v>
+      </c>
+      <c r="I4" s="63">
         <f>I5</f>
-        <v>46118</v>
-      </c>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="62">
+        <v>46132</v>
+      </c>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="65"/>
+      <c r="P4" s="63">
         <f>P5</f>
-        <v>46125</v>
-      </c>
-      <c r="Q4" s="63"/>
-      <c r="R4" s="63"/>
-      <c r="S4" s="63"/>
-      <c r="T4" s="63"/>
-      <c r="U4" s="63"/>
-      <c r="V4" s="64"/>
-      <c r="W4" s="62">
+        <v>46139</v>
+      </c>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="65"/>
+      <c r="W4" s="63">
         <f>W5</f>
-        <v>46132</v>
-      </c>
-      <c r="X4" s="63"/>
-      <c r="Y4" s="63"/>
-      <c r="Z4" s="63"/>
-      <c r="AA4" s="63"/>
-      <c r="AB4" s="63"/>
-      <c r="AC4" s="64"/>
-      <c r="AD4" s="62">
+        <v>46146</v>
+      </c>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="64"/>
+      <c r="Z4" s="64"/>
+      <c r="AA4" s="64"/>
+      <c r="AB4" s="64"/>
+      <c r="AC4" s="65"/>
+      <c r="AD4" s="63">
         <f>AD5</f>
-        <v>46139</v>
-      </c>
-      <c r="AE4" s="63"/>
-      <c r="AF4" s="63"/>
-      <c r="AG4" s="63"/>
-      <c r="AH4" s="63"/>
-      <c r="AI4" s="63"/>
-      <c r="AJ4" s="64"/>
-      <c r="AK4" s="62">
+        <v>46153</v>
+      </c>
+      <c r="AE4" s="64"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="64"/>
+      <c r="AH4" s="64"/>
+      <c r="AI4" s="64"/>
+      <c r="AJ4" s="65"/>
+      <c r="AK4" s="63">
         <f>AK5</f>
-        <v>46146</v>
-      </c>
-      <c r="AL4" s="63"/>
-      <c r="AM4" s="63"/>
-      <c r="AN4" s="63"/>
-      <c r="AO4" s="63"/>
-      <c r="AP4" s="63"/>
-      <c r="AQ4" s="64"/>
-      <c r="AR4" s="62">
+        <v>46160</v>
+      </c>
+      <c r="AL4" s="64"/>
+      <c r="AM4" s="64"/>
+      <c r="AN4" s="64"/>
+      <c r="AO4" s="64"/>
+      <c r="AP4" s="64"/>
+      <c r="AQ4" s="65"/>
+      <c r="AR4" s="63">
         <f>AR5</f>
-        <v>46153</v>
-      </c>
-      <c r="AS4" s="63"/>
-      <c r="AT4" s="63"/>
-      <c r="AU4" s="63"/>
-      <c r="AV4" s="63"/>
-      <c r="AW4" s="63"/>
-      <c r="AX4" s="64"/>
-      <c r="AY4" s="62">
+        <v>46167</v>
+      </c>
+      <c r="AS4" s="64"/>
+      <c r="AT4" s="64"/>
+      <c r="AU4" s="64"/>
+      <c r="AV4" s="64"/>
+      <c r="AW4" s="64"/>
+      <c r="AX4" s="65"/>
+      <c r="AY4" s="63">
         <f>AY5</f>
-        <v>46160</v>
-      </c>
-      <c r="AZ4" s="63"/>
-      <c r="BA4" s="63"/>
-      <c r="BB4" s="63"/>
-      <c r="BC4" s="63"/>
-      <c r="BD4" s="63"/>
-      <c r="BE4" s="64"/>
-      <c r="BF4" s="62">
+        <v>46174</v>
+      </c>
+      <c r="AZ4" s="64"/>
+      <c r="BA4" s="64"/>
+      <c r="BB4" s="64"/>
+      <c r="BC4" s="64"/>
+      <c r="BD4" s="64"/>
+      <c r="BE4" s="65"/>
+      <c r="BF4" s="63">
         <f>BF5</f>
-        <v>46167</v>
-      </c>
-      <c r="BG4" s="63"/>
-      <c r="BH4" s="63"/>
-      <c r="BI4" s="63"/>
-      <c r="BJ4" s="63"/>
-      <c r="BK4" s="63"/>
-      <c r="BL4" s="64"/>
-      <c r="BM4" s="62">
+        <v>46181</v>
+      </c>
+      <c r="BG4" s="64"/>
+      <c r="BH4" s="64"/>
+      <c r="BI4" s="64"/>
+      <c r="BJ4" s="64"/>
+      <c r="BK4" s="64"/>
+      <c r="BL4" s="65"/>
+      <c r="BM4" s="63">
         <f>BM5</f>
-        <v>46174</v>
-      </c>
-      <c r="BN4" s="63"/>
-      <c r="BO4" s="63"/>
-      <c r="BP4" s="63"/>
-      <c r="BQ4" s="63"/>
-      <c r="BR4" s="63"/>
-      <c r="BS4" s="64"/>
-      <c r="BT4" s="62">
+        <v>46188</v>
+      </c>
+      <c r="BN4" s="64"/>
+      <c r="BO4" s="64"/>
+      <c r="BP4" s="64"/>
+      <c r="BQ4" s="64"/>
+      <c r="BR4" s="64"/>
+      <c r="BS4" s="65"/>
+      <c r="BT4" s="63">
         <f>BT5</f>
-        <v>46181</v>
-      </c>
-      <c r="BU4" s="63"/>
-      <c r="BV4" s="63"/>
-      <c r="BW4" s="63"/>
-      <c r="BX4" s="63"/>
-      <c r="BY4" s="63"/>
-      <c r="BZ4" s="64"/>
-      <c r="CA4" s="62">
+        <v>46195</v>
+      </c>
+      <c r="BU4" s="64"/>
+      <c r="BV4" s="64"/>
+      <c r="BW4" s="64"/>
+      <c r="BX4" s="64"/>
+      <c r="BY4" s="64"/>
+      <c r="BZ4" s="65"/>
+      <c r="CA4" s="63">
         <f>CA5</f>
-        <v>46188</v>
-      </c>
-      <c r="CB4" s="63"/>
-      <c r="CC4" s="63"/>
-      <c r="CD4" s="63"/>
-      <c r="CE4" s="63"/>
-      <c r="CF4" s="63"/>
-      <c r="CG4" s="64"/>
-      <c r="CH4" s="62">
+        <v>46202</v>
+      </c>
+      <c r="CB4" s="64"/>
+      <c r="CC4" s="64"/>
+      <c r="CD4" s="64"/>
+      <c r="CE4" s="64"/>
+      <c r="CF4" s="64"/>
+      <c r="CG4" s="65"/>
+      <c r="CH4" s="63">
         <f>CH5</f>
-        <v>46195</v>
-      </c>
-      <c r="CI4" s="63"/>
-      <c r="CJ4" s="63"/>
-      <c r="CK4" s="63"/>
-      <c r="CL4" s="63"/>
-      <c r="CM4" s="63"/>
-      <c r="CN4" s="64"/>
-      <c r="CO4" s="62">
+        <v>46209</v>
+      </c>
+      <c r="CI4" s="64"/>
+      <c r="CJ4" s="64"/>
+      <c r="CK4" s="64"/>
+      <c r="CL4" s="64"/>
+      <c r="CM4" s="64"/>
+      <c r="CN4" s="65"/>
+      <c r="CO4" s="63">
         <f>CO5</f>
-        <v>46202</v>
-      </c>
-      <c r="CP4" s="63"/>
-      <c r="CQ4" s="63"/>
-      <c r="CR4" s="63"/>
-      <c r="CS4" s="63"/>
-      <c r="CT4" s="63"/>
-      <c r="CU4" s="64"/>
-      <c r="CV4" s="62">
+        <v>46216</v>
+      </c>
+      <c r="CP4" s="64"/>
+      <c r="CQ4" s="64"/>
+      <c r="CR4" s="64"/>
+      <c r="CS4" s="64"/>
+      <c r="CT4" s="64"/>
+      <c r="CU4" s="65"/>
+      <c r="CV4" s="63">
         <f>CV5</f>
-        <v>46209</v>
-      </c>
-      <c r="CW4" s="63"/>
-      <c r="CX4" s="63"/>
-      <c r="CY4" s="63"/>
-      <c r="CZ4" s="63"/>
-      <c r="DA4" s="63"/>
-      <c r="DB4" s="64"/>
-      <c r="DC4" s="62">
+        <v>46223</v>
+      </c>
+      <c r="CW4" s="64"/>
+      <c r="CX4" s="64"/>
+      <c r="CY4" s="64"/>
+      <c r="CZ4" s="64"/>
+      <c r="DA4" s="64"/>
+      <c r="DB4" s="65"/>
+      <c r="DC4" s="63">
         <f>DC5</f>
-        <v>46216</v>
-      </c>
-      <c r="DD4" s="63"/>
-      <c r="DE4" s="63"/>
-      <c r="DF4" s="63"/>
-      <c r="DG4" s="63"/>
-      <c r="DH4" s="63"/>
-      <c r="DI4" s="64"/>
-      <c r="DJ4" s="62">
+        <v>46230</v>
+      </c>
+      <c r="DD4" s="64"/>
+      <c r="DE4" s="64"/>
+      <c r="DF4" s="64"/>
+      <c r="DG4" s="64"/>
+      <c r="DH4" s="64"/>
+      <c r="DI4" s="65"/>
+      <c r="DJ4" s="63">
         <f>DJ5</f>
-        <v>46223</v>
-      </c>
-      <c r="DK4" s="63"/>
-      <c r="DL4" s="63"/>
-      <c r="DM4" s="63"/>
-      <c r="DN4" s="63"/>
-      <c r="DO4" s="63"/>
-      <c r="DP4" s="64"/>
-      <c r="DQ4" s="62">
+        <v>46237</v>
+      </c>
+      <c r="DK4" s="64"/>
+      <c r="DL4" s="64"/>
+      <c r="DM4" s="64"/>
+      <c r="DN4" s="64"/>
+      <c r="DO4" s="64"/>
+      <c r="DP4" s="65"/>
+      <c r="DQ4" s="63">
         <f>DQ5</f>
-        <v>46230</v>
-      </c>
-      <c r="DR4" s="63"/>
-      <c r="DS4" s="63"/>
-      <c r="DT4" s="63"/>
-      <c r="DU4" s="63"/>
-      <c r="DV4" s="63"/>
-      <c r="DW4" s="64"/>
-      <c r="DX4" s="62">
+        <v>46244</v>
+      </c>
+      <c r="DR4" s="64"/>
+      <c r="DS4" s="64"/>
+      <c r="DT4" s="64"/>
+      <c r="DU4" s="64"/>
+      <c r="DV4" s="64"/>
+      <c r="DW4" s="65"/>
+      <c r="DX4" s="63">
         <f>DX5</f>
-        <v>46237</v>
-      </c>
-      <c r="DY4" s="63"/>
-      <c r="DZ4" s="63"/>
-      <c r="EA4" s="63"/>
-      <c r="EB4" s="63"/>
-      <c r="EC4" s="63"/>
-      <c r="ED4" s="64"/>
-      <c r="EE4" s="62">
+        <v>46251</v>
+      </c>
+      <c r="DY4" s="64"/>
+      <c r="DZ4" s="64"/>
+      <c r="EA4" s="64"/>
+      <c r="EB4" s="64"/>
+      <c r="EC4" s="64"/>
+      <c r="ED4" s="65"/>
+      <c r="EE4" s="63">
         <f>EE5</f>
-        <v>46244</v>
-      </c>
-      <c r="EF4" s="63"/>
-      <c r="EG4" s="63"/>
-      <c r="EH4" s="63"/>
-      <c r="EI4" s="63"/>
-      <c r="EJ4" s="63"/>
-      <c r="EK4" s="64"/>
+        <v>46258</v>
+      </c>
+      <c r="EF4" s="64"/>
+      <c r="EG4" s="64"/>
+      <c r="EH4" s="64"/>
+      <c r="EI4" s="64"/>
+      <c r="EJ4" s="64"/>
+      <c r="EK4" s="65"/>
     </row>
     <row r="5" spans="1:141" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="G5" s="4"/>
       <c r="I5" s="29">
         <f>E2-WEEKDAY(E2,1)+2+7*(E4-1)</f>
-        <v>46118</v>
+        <v>46132</v>
       </c>
       <c r="J5" s="30">
         <f>I5+1</f>
-        <v>46119</v>
+        <v>46133</v>
       </c>
       <c r="K5" s="30">
         <f t="shared" ref="K5:AX5" si="0">J5+1</f>
-        <v>46120</v>
+        <v>46134</v>
       </c>
       <c r="L5" s="30">
         <f t="shared" si="0"/>
-        <v>46121</v>
+        <v>46135</v>
       </c>
       <c r="M5" s="30">
         <f t="shared" si="0"/>
-        <v>46122</v>
+        <v>46136</v>
       </c>
       <c r="N5" s="30">
         <f t="shared" si="0"/>
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="O5" s="31">
         <f t="shared" si="0"/>
-        <v>46124</v>
+        <v>46138</v>
       </c>
       <c r="P5" s="29">
         <f>O5+1</f>
-        <v>46125</v>
+        <v>46139</v>
       </c>
       <c r="Q5" s="30">
         <f>P5+1</f>
-        <v>46126</v>
+        <v>46140</v>
       </c>
       <c r="R5" s="30">
         <f t="shared" si="0"/>
-        <v>46127</v>
+        <v>46141</v>
       </c>
       <c r="S5" s="30">
         <f t="shared" si="0"/>
-        <v>46128</v>
+        <v>46142</v>
       </c>
       <c r="T5" s="30">
         <f t="shared" si="0"/>
-        <v>46129</v>
+        <v>46143</v>
       </c>
       <c r="U5" s="30">
         <f t="shared" si="0"/>
-        <v>46130</v>
+        <v>46144</v>
       </c>
       <c r="V5" s="31">
         <f t="shared" si="0"/>
-        <v>46131</v>
+        <v>46145</v>
       </c>
       <c r="W5" s="29">
         <f>V5+1</f>
-        <v>46132</v>
+        <v>46146</v>
       </c>
       <c r="X5" s="30">
         <f>W5+1</f>
-        <v>46133</v>
+        <v>46147</v>
       </c>
       <c r="Y5" s="30">
         <f t="shared" si="0"/>
-        <v>46134</v>
+        <v>46148</v>
       </c>
       <c r="Z5" s="30">
         <f t="shared" si="0"/>
-        <v>46135</v>
+        <v>46149</v>
       </c>
       <c r="AA5" s="30">
         <f t="shared" si="0"/>
-        <v>46136</v>
+        <v>46150</v>
       </c>
       <c r="AB5" s="30">
         <f t="shared" si="0"/>
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="AC5" s="31">
         <f t="shared" si="0"/>
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="AD5" s="29">
         <f>AC5+1</f>
-        <v>46139</v>
+        <v>46153</v>
       </c>
       <c r="AE5" s="30">
         <f>AD5+1</f>
-        <v>46140</v>
+        <v>46154</v>
       </c>
       <c r="AF5" s="30">
         <f t="shared" si="0"/>
-        <v>46141</v>
+        <v>46155</v>
       </c>
       <c r="AG5" s="30">
         <f t="shared" si="0"/>
-        <v>46142</v>
+        <v>46156</v>
       </c>
       <c r="AH5" s="30">
         <f t="shared" si="0"/>
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="AI5" s="30">
         <f t="shared" si="0"/>
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="AJ5" s="31">
         <f t="shared" si="0"/>
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="AK5" s="29">
         <f>AJ5+1</f>
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="AL5" s="30">
         <f>AK5+1</f>
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="AM5" s="30">
         <f t="shared" si="0"/>
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="AN5" s="30">
         <f t="shared" si="0"/>
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="AO5" s="30">
         <f t="shared" si="0"/>
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="AP5" s="30">
         <f t="shared" si="0"/>
-        <v>46151</v>
+        <v>46165</v>
       </c>
       <c r="AQ5" s="31">
         <f t="shared" si="0"/>
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="AR5" s="29">
         <f>AQ5+1</f>
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="AS5" s="30">
         <f>AR5+1</f>
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="AT5" s="30">
         <f t="shared" si="0"/>
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="AU5" s="30">
         <f t="shared" si="0"/>
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="AV5" s="30">
         <f t="shared" si="0"/>
-        <v>46157</v>
+        <v>46171</v>
       </c>
       <c r="AW5" s="30">
         <f t="shared" si="0"/>
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="AX5" s="31">
         <f t="shared" si="0"/>
-        <v>46159</v>
+        <v>46173</v>
       </c>
       <c r="AY5" s="29">
         <f t="shared" ref="AY5:CD5" si="1">AX5+1</f>
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="AZ5" s="30">
         <f t="shared" si="1"/>
-        <v>46161</v>
+        <v>46175</v>
       </c>
       <c r="BA5" s="30">
         <f t="shared" si="1"/>
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="BB5" s="30">
         <f t="shared" si="1"/>
-        <v>46163</v>
+        <v>46177</v>
       </c>
       <c r="BC5" s="30">
         <f t="shared" si="1"/>
-        <v>46164</v>
+        <v>46178</v>
       </c>
       <c r="BD5" s="30">
         <f t="shared" si="1"/>
-        <v>46165</v>
+        <v>46179</v>
       </c>
       <c r="BE5" s="31">
         <f t="shared" si="1"/>
-        <v>46166</v>
+        <v>46180</v>
       </c>
       <c r="BF5" s="29">
         <f t="shared" si="1"/>
-        <v>46167</v>
+        <v>46181</v>
       </c>
       <c r="BG5" s="30">
         <f t="shared" si="1"/>
-        <v>46168</v>
+        <v>46182</v>
       </c>
       <c r="BH5" s="30">
         <f t="shared" si="1"/>
-        <v>46169</v>
+        <v>46183</v>
       </c>
       <c r="BI5" s="30">
         <f t="shared" si="1"/>
-        <v>46170</v>
+        <v>46184</v>
       </c>
       <c r="BJ5" s="30">
         <f t="shared" si="1"/>
-        <v>46171</v>
+        <v>46185</v>
       </c>
       <c r="BK5" s="30">
         <f t="shared" si="1"/>
-        <v>46172</v>
+        <v>46186</v>
       </c>
       <c r="BL5" s="31">
         <f t="shared" si="1"/>
-        <v>46173</v>
+        <v>46187</v>
       </c>
       <c r="BM5" s="29">
         <f t="shared" si="1"/>
-        <v>46174</v>
+        <v>46188</v>
       </c>
       <c r="BN5" s="30">
         <f t="shared" si="1"/>
-        <v>46175</v>
+        <v>46189</v>
       </c>
       <c r="BO5" s="30">
         <f t="shared" si="1"/>
-        <v>46176</v>
+        <v>46190</v>
       </c>
       <c r="BP5" s="30">
         <f t="shared" si="1"/>
-        <v>46177</v>
+        <v>46191</v>
       </c>
       <c r="BQ5" s="30">
         <f t="shared" si="1"/>
-        <v>46178</v>
+        <v>46192</v>
       </c>
       <c r="BR5" s="30">
         <f t="shared" si="1"/>
-        <v>46179</v>
+        <v>46193</v>
       </c>
       <c r="BS5" s="31">
         <f t="shared" si="1"/>
-        <v>46180</v>
+        <v>46194</v>
       </c>
       <c r="BT5" s="29">
         <f t="shared" si="1"/>
-        <v>46181</v>
+        <v>46195</v>
       </c>
       <c r="BU5" s="30">
         <f t="shared" si="1"/>
-        <v>46182</v>
+        <v>46196</v>
       </c>
       <c r="BV5" s="30">
         <f t="shared" si="1"/>
-        <v>46183</v>
+        <v>46197</v>
       </c>
       <c r="BW5" s="30">
         <f t="shared" si="1"/>
-        <v>46184</v>
+        <v>46198</v>
       </c>
       <c r="BX5" s="30">
         <f t="shared" si="1"/>
-        <v>46185</v>
+        <v>46199</v>
       </c>
       <c r="BY5" s="30">
         <f t="shared" si="1"/>
-        <v>46186</v>
+        <v>46200</v>
       </c>
       <c r="BZ5" s="31">
         <f t="shared" si="1"/>
-        <v>46187</v>
+        <v>46201</v>
       </c>
       <c r="CA5" s="29">
         <f t="shared" si="1"/>
-        <v>46188</v>
+        <v>46202</v>
       </c>
       <c r="CB5" s="30">
         <f t="shared" si="1"/>
-        <v>46189</v>
+        <v>46203</v>
       </c>
       <c r="CC5" s="30">
         <f t="shared" si="1"/>
-        <v>46190</v>
+        <v>46204</v>
       </c>
       <c r="CD5" s="30">
         <f t="shared" si="1"/>
-        <v>46191</v>
+        <v>46205</v>
       </c>
       <c r="CE5" s="30">
         <f t="shared" ref="CE5:DJ5" si="2">CD5+1</f>
-        <v>46192</v>
+        <v>46206</v>
       </c>
       <c r="CF5" s="30">
         <f t="shared" si="2"/>
-        <v>46193</v>
+        <v>46207</v>
       </c>
       <c r="CG5" s="31">
         <f t="shared" si="2"/>
-        <v>46194</v>
+        <v>46208</v>
       </c>
       <c r="CH5" s="29">
         <f t="shared" si="2"/>
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="CI5" s="30">
         <f t="shared" si="2"/>
-        <v>46196</v>
+        <v>46210</v>
       </c>
       <c r="CJ5" s="30">
         <f t="shared" si="2"/>
-        <v>46197</v>
+        <v>46211</v>
       </c>
       <c r="CK5" s="30">
         <f t="shared" si="2"/>
-        <v>46198</v>
+        <v>46212</v>
       </c>
       <c r="CL5" s="30">
         <f t="shared" si="2"/>
-        <v>46199</v>
+        <v>46213</v>
       </c>
       <c r="CM5" s="30">
         <f t="shared" si="2"/>
-        <v>46200</v>
+        <v>46214</v>
       </c>
       <c r="CN5" s="31">
         <f t="shared" si="2"/>
-        <v>46201</v>
+        <v>46215</v>
       </c>
       <c r="CO5" s="29">
         <f t="shared" si="2"/>
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="CP5" s="30">
         <f t="shared" si="2"/>
-        <v>46203</v>
+        <v>46217</v>
       </c>
       <c r="CQ5" s="30">
         <f t="shared" si="2"/>
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="CR5" s="30">
         <f t="shared" si="2"/>
-        <v>46205</v>
+        <v>46219</v>
       </c>
       <c r="CS5" s="30">
         <f t="shared" si="2"/>
-        <v>46206</v>
+        <v>46220</v>
       </c>
       <c r="CT5" s="30">
         <f t="shared" si="2"/>
-        <v>46207</v>
+        <v>46221</v>
       </c>
       <c r="CU5" s="31">
         <f t="shared" si="2"/>
-        <v>46208</v>
+        <v>46222</v>
       </c>
       <c r="CV5" s="29">
         <f t="shared" si="2"/>
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="CW5" s="30">
         <f t="shared" si="2"/>
-        <v>46210</v>
+        <v>46224</v>
       </c>
       <c r="CX5" s="30">
         <f t="shared" si="2"/>
-        <v>46211</v>
+        <v>46225</v>
       </c>
       <c r="CY5" s="30">
         <f t="shared" si="2"/>
-        <v>46212</v>
+        <v>46226</v>
       </c>
       <c r="CZ5" s="30">
         <f t="shared" si="2"/>
-        <v>46213</v>
+        <v>46227</v>
       </c>
       <c r="DA5" s="30">
         <f t="shared" si="2"/>
-        <v>46214</v>
+        <v>46228</v>
       </c>
       <c r="DB5" s="31">
         <f t="shared" si="2"/>
-        <v>46215</v>
+        <v>46229</v>
       </c>
       <c r="DC5" s="29">
         <f t="shared" si="2"/>
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="DD5" s="30">
         <f t="shared" si="2"/>
-        <v>46217</v>
+        <v>46231</v>
       </c>
       <c r="DE5" s="30">
         <f t="shared" si="2"/>
-        <v>46218</v>
+        <v>46232</v>
       </c>
       <c r="DF5" s="30">
         <f t="shared" si="2"/>
-        <v>46219</v>
+        <v>46233</v>
       </c>
       <c r="DG5" s="30">
         <f t="shared" si="2"/>
-        <v>46220</v>
+        <v>46234</v>
       </c>
       <c r="DH5" s="30">
         <f t="shared" si="2"/>
-        <v>46221</v>
+        <v>46235</v>
       </c>
       <c r="DI5" s="31">
         <f t="shared" si="2"/>
-        <v>46222</v>
+        <v>46236</v>
       </c>
       <c r="DJ5" s="29">
         <f t="shared" si="2"/>
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="DK5" s="30">
         <f t="shared" ref="DK5:EK5" si="3">DJ5+1</f>
-        <v>46224</v>
+        <v>46238</v>
       </c>
       <c r="DL5" s="30">
         <f t="shared" si="3"/>
-        <v>46225</v>
+        <v>46239</v>
       </c>
       <c r="DM5" s="30">
         <f t="shared" si="3"/>
-        <v>46226</v>
+        <v>46240</v>
       </c>
       <c r="DN5" s="30">
         <f t="shared" si="3"/>
-        <v>46227</v>
+        <v>46241</v>
       </c>
       <c r="DO5" s="30">
         <f t="shared" si="3"/>
-        <v>46228</v>
+        <v>46242</v>
       </c>
       <c r="DP5" s="31">
         <f t="shared" si="3"/>
-        <v>46229</v>
+        <v>46243</v>
       </c>
       <c r="DQ5" s="29">
         <f t="shared" si="3"/>
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="DR5" s="30">
         <f t="shared" si="3"/>
-        <v>46231</v>
+        <v>46245</v>
       </c>
       <c r="DS5" s="30">
         <f t="shared" si="3"/>
-        <v>46232</v>
+        <v>46246</v>
       </c>
       <c r="DT5" s="30">
         <f t="shared" si="3"/>
-        <v>46233</v>
+        <v>46247</v>
       </c>
       <c r="DU5" s="30">
         <f t="shared" si="3"/>
-        <v>46234</v>
+        <v>46248</v>
       </c>
       <c r="DV5" s="30">
         <f t="shared" si="3"/>
-        <v>46235</v>
+        <v>46249</v>
       </c>
       <c r="DW5" s="31">
         <f t="shared" si="3"/>
-        <v>46236</v>
+        <v>46250</v>
       </c>
       <c r="DX5" s="29">
         <f t="shared" si="3"/>
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="DY5" s="30">
         <f t="shared" si="3"/>
-        <v>46238</v>
+        <v>46252</v>
       </c>
       <c r="DZ5" s="30">
         <f t="shared" si="3"/>
-        <v>46239</v>
+        <v>46253</v>
       </c>
       <c r="EA5" s="30">
         <f t="shared" si="3"/>
-        <v>46240</v>
+        <v>46254</v>
       </c>
       <c r="EB5" s="30">
         <f t="shared" si="3"/>
-        <v>46241</v>
+        <v>46255</v>
       </c>
       <c r="EC5" s="30">
         <f t="shared" si="3"/>
-        <v>46242</v>
+        <v>46256</v>
       </c>
       <c r="ED5" s="31">
         <f t="shared" si="3"/>
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="EE5" s="29">
         <f t="shared" si="3"/>
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="EF5" s="30">
         <f t="shared" si="3"/>
-        <v>46245</v>
+        <v>46259</v>
       </c>
       <c r="EG5" s="30">
         <f t="shared" si="3"/>
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="EH5" s="30">
         <f t="shared" si="3"/>
-        <v>46247</v>
+        <v>46261</v>
       </c>
       <c r="EI5" s="30">
         <f t="shared" si="3"/>
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="EJ5" s="30">
         <f t="shared" si="3"/>
-        <v>46249</v>
+        <v>46263</v>
       </c>
       <c r="EK5" s="31">
         <f t="shared" si="3"/>
-        <v>46250</v>
+        <v>46264</v>
       </c>
     </row>
     <row r="6" spans="1:141" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -2814,14 +2814,14 @@
     </row>
     <row r="7" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
       <c r="H7" s="40" t="str">
         <f t="shared" ref="H7:H27" si="8">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
@@ -4035,14 +4035,14 @@
     </row>
     <row r="15" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
+      <c r="G15" s="62"/>
       <c r="H15" s="40" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4190,7 +4190,7 @@
         <v>61</v>
       </c>
       <c r="D16" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="38">
         <v>46125</v>
@@ -4346,7 +4346,7 @@
         <v>62</v>
       </c>
       <c r="D17" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E17" s="38">
         <v>46125</v>
@@ -4502,7 +4502,7 @@
         <v>60</v>
       </c>
       <c r="D18" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E18" s="38">
         <v>46125</v>
@@ -4658,7 +4658,7 @@
         <v>25</v>
       </c>
       <c r="D19" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E19" s="38">
         <v>46125</v>
@@ -4947,14 +4947,14 @@
     </row>
     <row r="21" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="65"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
       <c r="H21" s="40" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -5102,7 +5102,7 @@
         <v>60</v>
       </c>
       <c r="D22" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E22" s="39">
         <v>46132</v>
@@ -5258,7 +5258,7 @@
         <v>62</v>
       </c>
       <c r="D23" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="39">
         <v>46132</v>
@@ -5414,7 +5414,7 @@
         <v>61</v>
       </c>
       <c r="D24" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" s="39">
         <v>46132</v>
@@ -5570,7 +5570,7 @@
         <v>26</v>
       </c>
       <c r="D25" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" s="39">
         <v>46132</v>
@@ -5726,7 +5726,7 @@
         <v>25</v>
       </c>
       <c r="D26" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="39">
         <v>46132</v>
@@ -5882,7 +5882,7 @@
         <v>25</v>
       </c>
       <c r="D27" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="39">
         <v>46132</v>
@@ -6177,14 +6177,14 @@
     </row>
     <row r="29" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="65" t="s">
+      <c r="B29" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
       <c r="H29" s="40" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -6332,7 +6332,7 @@
         <v>61</v>
       </c>
       <c r="D30" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30" s="39">
         <v>46139</v>
@@ -6488,7 +6488,7 @@
         <v>64</v>
       </c>
       <c r="D31" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E31" s="39">
         <v>46139</v>
@@ -6644,7 +6644,7 @@
         <v>25</v>
       </c>
       <c r="D32" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" s="39">
         <v>46139</v>
@@ -6800,7 +6800,7 @@
         <v>25</v>
       </c>
       <c r="D33" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E33" s="39">
         <v>46139</v>
@@ -7250,7 +7250,7 @@
         <v>61</v>
       </c>
       <c r="D36" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E36" s="38">
         <v>46146</v>
@@ -7403,7 +7403,7 @@
         <v>64</v>
       </c>
       <c r="D37" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" s="38">
         <v>46146</v>
@@ -7556,7 +7556,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="37">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="E38" s="38">
         <v>46146</v>

--- a/Group 5_ CMARCH1_GanttChart.xlsx
+++ b/Group 5_ CMARCH1_GanttChart.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\PortableGit\assembly-language-color-code-guessing-game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1741AE24-B46C-432F-A973-19F484046BFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7151C238-8B69-466F-B6E1-E4F87E4E794E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -872,9 +872,6 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -886,6 +883,9 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1475,27 +1475,27 @@
       <c r="F1" s="19"/>
       <c r="H1" s="1"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="66" t="b">
+      <c r="J1" s="65" t="b">
         <f>B3=HYPERLINK("https://vertex42.link/HowToMakeAGanttChart","► Watch How to Make a Gantt Chart in Excel")</f>
         <v>0</v>
       </c>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="P1" s="66"/>
-      <c r="Q1" s="66"/>
-      <c r="R1" s="66"/>
-      <c r="S1" s="66"/>
-      <c r="T1" s="66"/>
-      <c r="U1" s="66"/>
-      <c r="V1" s="66"/>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="66"/>
-      <c r="Z1" s="66"/>
-      <c r="AA1" s="66"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="X1" s="65"/>
+      <c r="Y1" s="65"/>
+      <c r="Z1" s="65"/>
+      <c r="AA1" s="65"/>
     </row>
     <row r="2" spans="1:141" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="33" t="s">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E3" s="25">
         <f ca="1">TODAY()</f>
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="F3" s="26"/>
     </row>
@@ -1531,196 +1531,196 @@
       <c r="E4" s="24">
         <v>3</v>
       </c>
-      <c r="I4" s="63">
+      <c r="I4" s="62">
         <f>I5</f>
         <v>46132</v>
       </c>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="65"/>
-      <c r="P4" s="63">
+      <c r="J4" s="63"/>
+      <c r="K4" s="63"/>
+      <c r="L4" s="63"/>
+      <c r="M4" s="63"/>
+      <c r="N4" s="63"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="62">
         <f>P5</f>
         <v>46139</v>
       </c>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
-      <c r="U4" s="64"/>
-      <c r="V4" s="65"/>
-      <c r="W4" s="63">
+      <c r="Q4" s="63"/>
+      <c r="R4" s="63"/>
+      <c r="S4" s="63"/>
+      <c r="T4" s="63"/>
+      <c r="U4" s="63"/>
+      <c r="V4" s="64"/>
+      <c r="W4" s="62">
         <f>W5</f>
         <v>46146</v>
       </c>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="64"/>
-      <c r="Z4" s="64"/>
-      <c r="AA4" s="64"/>
-      <c r="AB4" s="64"/>
-      <c r="AC4" s="65"/>
-      <c r="AD4" s="63">
+      <c r="X4" s="63"/>
+      <c r="Y4" s="63"/>
+      <c r="Z4" s="63"/>
+      <c r="AA4" s="63"/>
+      <c r="AB4" s="63"/>
+      <c r="AC4" s="64"/>
+      <c r="AD4" s="62">
         <f>AD5</f>
         <v>46153</v>
       </c>
-      <c r="AE4" s="64"/>
-      <c r="AF4" s="64"/>
-      <c r="AG4" s="64"/>
-      <c r="AH4" s="64"/>
-      <c r="AI4" s="64"/>
-      <c r="AJ4" s="65"/>
-      <c r="AK4" s="63">
+      <c r="AE4" s="63"/>
+      <c r="AF4" s="63"/>
+      <c r="AG4" s="63"/>
+      <c r="AH4" s="63"/>
+      <c r="AI4" s="63"/>
+      <c r="AJ4" s="64"/>
+      <c r="AK4" s="62">
         <f>AK5</f>
         <v>46160</v>
       </c>
-      <c r="AL4" s="64"/>
-      <c r="AM4" s="64"/>
-      <c r="AN4" s="64"/>
-      <c r="AO4" s="64"/>
-      <c r="AP4" s="64"/>
-      <c r="AQ4" s="65"/>
-      <c r="AR4" s="63">
+      <c r="AL4" s="63"/>
+      <c r="AM4" s="63"/>
+      <c r="AN4" s="63"/>
+      <c r="AO4" s="63"/>
+      <c r="AP4" s="63"/>
+      <c r="AQ4" s="64"/>
+      <c r="AR4" s="62">
         <f>AR5</f>
         <v>46167</v>
       </c>
-      <c r="AS4" s="64"/>
-      <c r="AT4" s="64"/>
-      <c r="AU4" s="64"/>
-      <c r="AV4" s="64"/>
-      <c r="AW4" s="64"/>
-      <c r="AX4" s="65"/>
-      <c r="AY4" s="63">
+      <c r="AS4" s="63"/>
+      <c r="AT4" s="63"/>
+      <c r="AU4" s="63"/>
+      <c r="AV4" s="63"/>
+      <c r="AW4" s="63"/>
+      <c r="AX4" s="64"/>
+      <c r="AY4" s="62">
         <f>AY5</f>
         <v>46174</v>
       </c>
-      <c r="AZ4" s="64"/>
-      <c r="BA4" s="64"/>
-      <c r="BB4" s="64"/>
-      <c r="BC4" s="64"/>
-      <c r="BD4" s="64"/>
-      <c r="BE4" s="65"/>
-      <c r="BF4" s="63">
+      <c r="AZ4" s="63"/>
+      <c r="BA4" s="63"/>
+      <c r="BB4" s="63"/>
+      <c r="BC4" s="63"/>
+      <c r="BD4" s="63"/>
+      <c r="BE4" s="64"/>
+      <c r="BF4" s="62">
         <f>BF5</f>
         <v>46181</v>
       </c>
-      <c r="BG4" s="64"/>
-      <c r="BH4" s="64"/>
-      <c r="BI4" s="64"/>
-      <c r="BJ4" s="64"/>
-      <c r="BK4" s="64"/>
-      <c r="BL4" s="65"/>
-      <c r="BM4" s="63">
+      <c r="BG4" s="63"/>
+      <c r="BH4" s="63"/>
+      <c r="BI4" s="63"/>
+      <c r="BJ4" s="63"/>
+      <c r="BK4" s="63"/>
+      <c r="BL4" s="64"/>
+      <c r="BM4" s="62">
         <f>BM5</f>
         <v>46188</v>
       </c>
-      <c r="BN4" s="64"/>
-      <c r="BO4" s="64"/>
-      <c r="BP4" s="64"/>
-      <c r="BQ4" s="64"/>
-      <c r="BR4" s="64"/>
-      <c r="BS4" s="65"/>
-      <c r="BT4" s="63">
+      <c r="BN4" s="63"/>
+      <c r="BO4" s="63"/>
+      <c r="BP4" s="63"/>
+      <c r="BQ4" s="63"/>
+      <c r="BR4" s="63"/>
+      <c r="BS4" s="64"/>
+      <c r="BT4" s="62">
         <f>BT5</f>
         <v>46195</v>
       </c>
-      <c r="BU4" s="64"/>
-      <c r="BV4" s="64"/>
-      <c r="BW4" s="64"/>
-      <c r="BX4" s="64"/>
-      <c r="BY4" s="64"/>
-      <c r="BZ4" s="65"/>
-      <c r="CA4" s="63">
+      <c r="BU4" s="63"/>
+      <c r="BV4" s="63"/>
+      <c r="BW4" s="63"/>
+      <c r="BX4" s="63"/>
+      <c r="BY4" s="63"/>
+      <c r="BZ4" s="64"/>
+      <c r="CA4" s="62">
         <f>CA5</f>
         <v>46202</v>
       </c>
-      <c r="CB4" s="64"/>
-      <c r="CC4" s="64"/>
-      <c r="CD4" s="64"/>
-      <c r="CE4" s="64"/>
-      <c r="CF4" s="64"/>
-      <c r="CG4" s="65"/>
-      <c r="CH4" s="63">
+      <c r="CB4" s="63"/>
+      <c r="CC4" s="63"/>
+      <c r="CD4" s="63"/>
+      <c r="CE4" s="63"/>
+      <c r="CF4" s="63"/>
+      <c r="CG4" s="64"/>
+      <c r="CH4" s="62">
         <f>CH5</f>
         <v>46209</v>
       </c>
-      <c r="CI4" s="64"/>
-      <c r="CJ4" s="64"/>
-      <c r="CK4" s="64"/>
-      <c r="CL4" s="64"/>
-      <c r="CM4" s="64"/>
-      <c r="CN4" s="65"/>
-      <c r="CO4" s="63">
+      <c r="CI4" s="63"/>
+      <c r="CJ4" s="63"/>
+      <c r="CK4" s="63"/>
+      <c r="CL4" s="63"/>
+      <c r="CM4" s="63"/>
+      <c r="CN4" s="64"/>
+      <c r="CO4" s="62">
         <f>CO5</f>
         <v>46216</v>
       </c>
-      <c r="CP4" s="64"/>
-      <c r="CQ4" s="64"/>
-      <c r="CR4" s="64"/>
-      <c r="CS4" s="64"/>
-      <c r="CT4" s="64"/>
-      <c r="CU4" s="65"/>
-      <c r="CV4" s="63">
+      <c r="CP4" s="63"/>
+      <c r="CQ4" s="63"/>
+      <c r="CR4" s="63"/>
+      <c r="CS4" s="63"/>
+      <c r="CT4" s="63"/>
+      <c r="CU4" s="64"/>
+      <c r="CV4" s="62">
         <f>CV5</f>
         <v>46223</v>
       </c>
-      <c r="CW4" s="64"/>
-      <c r="CX4" s="64"/>
-      <c r="CY4" s="64"/>
-      <c r="CZ4" s="64"/>
-      <c r="DA4" s="64"/>
-      <c r="DB4" s="65"/>
-      <c r="DC4" s="63">
+      <c r="CW4" s="63"/>
+      <c r="CX4" s="63"/>
+      <c r="CY4" s="63"/>
+      <c r="CZ4" s="63"/>
+      <c r="DA4" s="63"/>
+      <c r="DB4" s="64"/>
+      <c r="DC4" s="62">
         <f>DC5</f>
         <v>46230</v>
       </c>
-      <c r="DD4" s="64"/>
-      <c r="DE4" s="64"/>
-      <c r="DF4" s="64"/>
-      <c r="DG4" s="64"/>
-      <c r="DH4" s="64"/>
-      <c r="DI4" s="65"/>
-      <c r="DJ4" s="63">
+      <c r="DD4" s="63"/>
+      <c r="DE4" s="63"/>
+      <c r="DF4" s="63"/>
+      <c r="DG4" s="63"/>
+      <c r="DH4" s="63"/>
+      <c r="DI4" s="64"/>
+      <c r="DJ4" s="62">
         <f>DJ5</f>
         <v>46237</v>
       </c>
-      <c r="DK4" s="64"/>
-      <c r="DL4" s="64"/>
-      <c r="DM4" s="64"/>
-      <c r="DN4" s="64"/>
-      <c r="DO4" s="64"/>
-      <c r="DP4" s="65"/>
-      <c r="DQ4" s="63">
+      <c r="DK4" s="63"/>
+      <c r="DL4" s="63"/>
+      <c r="DM4" s="63"/>
+      <c r="DN4" s="63"/>
+      <c r="DO4" s="63"/>
+      <c r="DP4" s="64"/>
+      <c r="DQ4" s="62">
         <f>DQ5</f>
         <v>46244</v>
       </c>
-      <c r="DR4" s="64"/>
-      <c r="DS4" s="64"/>
-      <c r="DT4" s="64"/>
-      <c r="DU4" s="64"/>
-      <c r="DV4" s="64"/>
-      <c r="DW4" s="65"/>
-      <c r="DX4" s="63">
+      <c r="DR4" s="63"/>
+      <c r="DS4" s="63"/>
+      <c r="DT4" s="63"/>
+      <c r="DU4" s="63"/>
+      <c r="DV4" s="63"/>
+      <c r="DW4" s="64"/>
+      <c r="DX4" s="62">
         <f>DX5</f>
         <v>46251</v>
       </c>
-      <c r="DY4" s="64"/>
-      <c r="DZ4" s="64"/>
-      <c r="EA4" s="64"/>
-      <c r="EB4" s="64"/>
-      <c r="EC4" s="64"/>
-      <c r="ED4" s="65"/>
-      <c r="EE4" s="63">
+      <c r="DY4" s="63"/>
+      <c r="DZ4" s="63"/>
+      <c r="EA4" s="63"/>
+      <c r="EB4" s="63"/>
+      <c r="EC4" s="63"/>
+      <c r="ED4" s="64"/>
+      <c r="EE4" s="62">
         <f>EE5</f>
         <v>46258</v>
       </c>
-      <c r="EF4" s="64"/>
-      <c r="EG4" s="64"/>
-      <c r="EH4" s="64"/>
-      <c r="EI4" s="64"/>
-      <c r="EJ4" s="64"/>
-      <c r="EK4" s="65"/>
+      <c r="EF4" s="63"/>
+      <c r="EG4" s="63"/>
+      <c r="EH4" s="63"/>
+      <c r="EI4" s="63"/>
+      <c r="EJ4" s="63"/>
+      <c r="EK4" s="64"/>
     </row>
     <row r="5" spans="1:141" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
@@ -2814,14 +2814,14 @@
     </row>
     <row r="7" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
-      <c r="B7" s="62" t="s">
+      <c r="B7" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="62"/>
-      <c r="E7" s="62"/>
-      <c r="F7" s="62"/>
-      <c r="G7" s="62"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="66"/>
       <c r="H7" s="40" t="str">
         <f t="shared" ref="H7:H27" si="8">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
@@ -4035,14 +4035,14 @@
     </row>
     <row r="15" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A15" s="7"/>
-      <c r="B15" s="62" t="s">
+      <c r="B15" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="62"/>
-      <c r="D15" s="62"/>
-      <c r="E15" s="62"/>
-      <c r="F15" s="62"/>
-      <c r="G15" s="62"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
       <c r="H15" s="40" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -4947,14 +4947,14 @@
     </row>
     <row r="21" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
-      <c r="B21" s="62" t="s">
+      <c r="B21" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="62"/>
-      <c r="E21" s="62"/>
-      <c r="F21" s="62"/>
-      <c r="G21" s="62"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
       <c r="H21" s="40" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -6177,14 +6177,14 @@
     </row>
     <row r="29" spans="1:141" s="42" customFormat="1" ht="21" x14ac:dyDescent="0.25">
       <c r="A29" s="7"/>
-      <c r="B29" s="62" t="s">
+      <c r="B29" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="62"/>
-      <c r="E29" s="62"/>
-      <c r="F29" s="62"/>
-      <c r="G29" s="62"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="66"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="66"/>
+      <c r="G29" s="66"/>
       <c r="H29" s="40" t="str">
         <f t="shared" si="9"/>
         <v/>
@@ -7556,7 +7556,7 @@
         <v>26</v>
       </c>
       <c r="D38" s="37">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="E38" s="38">
         <v>46146</v>
@@ -7709,7 +7709,7 @@
         <v>25</v>
       </c>
       <c r="D39" s="37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="38">
         <v>46146</v>
@@ -8764,22 +8764,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="EE4:EK4"/>
-    <mergeCell ref="CV4:DB4"/>
-    <mergeCell ref="DC4:DI4"/>
-    <mergeCell ref="DJ4:DP4"/>
-    <mergeCell ref="DQ4:DW4"/>
-    <mergeCell ref="DX4:ED4"/>
-    <mergeCell ref="BM4:BS4"/>
-    <mergeCell ref="BT4:BZ4"/>
-    <mergeCell ref="CA4:CG4"/>
-    <mergeCell ref="CH4:CN4"/>
-    <mergeCell ref="CO4:CU4"/>
-    <mergeCell ref="J1:AA1"/>
-    <mergeCell ref="AK4:AQ4"/>
-    <mergeCell ref="AR4:AX4"/>
-    <mergeCell ref="AY4:BE4"/>
-    <mergeCell ref="B7:G7"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B21:G21"/>
     <mergeCell ref="B29:G29"/>
@@ -8788,6 +8772,22 @@
     <mergeCell ref="P4:V4"/>
     <mergeCell ref="W4:AC4"/>
     <mergeCell ref="AD4:AJ4"/>
+    <mergeCell ref="J1:AA1"/>
+    <mergeCell ref="AK4:AQ4"/>
+    <mergeCell ref="AR4:AX4"/>
+    <mergeCell ref="AY4:BE4"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="BM4:BS4"/>
+    <mergeCell ref="BT4:BZ4"/>
+    <mergeCell ref="CA4:CG4"/>
+    <mergeCell ref="CH4:CN4"/>
+    <mergeCell ref="CO4:CU4"/>
+    <mergeCell ref="EE4:EK4"/>
+    <mergeCell ref="CV4:DB4"/>
+    <mergeCell ref="DC4:DI4"/>
+    <mergeCell ref="DJ4:DP4"/>
+    <mergeCell ref="DQ4:DW4"/>
+    <mergeCell ref="DX4:ED4"/>
   </mergeCells>
   <conditionalFormatting sqref="D16:D20 D8:D14 D30:D45 D22:D28">
     <cfRule type="dataBar" priority="46">
